--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47B.xlsx
@@ -103,7 +103,7 @@
     <t>Fecha de término del periodo que se informa</t>
   </si>
   <si>
-    <t>Temática de las preguntas frecuentes</t>
+    <t>Temática de las preguntas frecuentes (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Planteamiento de las preguntas frecuentes</t>
@@ -130,28 +130,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>FCAE431F5274F86C0729CA279A934BF0</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>Unidad de Transparencia</t>
-  </si>
-  <si>
-    <t>16/11/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de julio del 2022 al 30 de septiembre del 2022, el Colegio de Bachilleres del Estado de Tlaxcala no se generó política en referencia a este tema.</t>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>30B2BDF4FD0C1D54C47A2CAEC5F8B87F</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>11/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de julio del 2023 al 30 de septiembre del 2023, el Colegio de Bachilleres del Estado de Tlaxcala, de acuerdo al artículo 63, fracción XLVII, no generó política en referencia a este tema.</t>
   </si>
 </sst>
 </file>
@@ -551,7 +551,7 @@
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="66.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="53.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40.7109375" bestFit="1" customWidth="1"/>
@@ -559,7 +559,7 @@
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="255" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="176" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -732,16 +732,16 @@
     </row>
     <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>39</v>
@@ -759,7 +759,7 @@
         <v>39</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>44</v>
